--- a/src/tests/data/resources/OrangeHRM Requirements.xlsx
+++ b/src/tests/data/resources/OrangeHRM Requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\YT Classes and Practice\AI-framework-playwright\src\tests\data\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEA4E8A-8030-4B26-BEFF-F869A8354E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C087F3-2D12-433C-A5C0-20B02BFF7C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{5B534653-ECC6-452B-97EB-7FFE7785091D}"/>
   </bookViews>
